--- a/evac_by_zip/evac_by_zip_2026-08-20.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-20.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 267 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 360 addresses (across 2 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>598</v>
+        <v>185</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -980,17 +980,17 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>36</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1048,62 +1048,60 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>225</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>No named fire</t>
+      <c r="E16" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E17" s="10" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1112,7 +1110,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1124,14 +1122,14 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -1139,7 +1137,7 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>231</v>
+        <v>57</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1148,26 +1146,26 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
@@ -1175,7 +1173,7 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1184,26 +1182,26 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1220,34 +1218,36 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>15</v>
-      </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>3001</v>
+        <v>3014</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>669</v>
+        <v>1018</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>865</v>
+        <v>410</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>4535</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="28">
@@ -1446,13 +1446,13 @@
         <v>198</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>267</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>3199</v>
+        <v>3212</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>702</v>
+        <v>1159</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>901</v>
+        <v>431</v>
       </c>
       <c r="E29" s="18" t="n">
         <v>4802</v>
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-119-B</t>
+          <t>US-OR-UMA-UMC-1406020</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-155-A</t>
+          <t>US-OR-UMA-UMC-157</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="G13" s="21" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406020</t>
+          <t>US-OR-UMA-UMC-123-E</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="G14" s="21" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-D</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G15" s="21" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G16" s="21" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-157</t>
+          <t>US-OR-UMA-UMC-1406017-A</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -2063,11 +2063,11 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G17" s="21" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-121-A</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -2098,11 +2098,11 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G18" s="21" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-E</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="G19" s="21" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UMA-UMC-243</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="G20" s="21" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -2203,396 +2203,396 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G21" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-119-B</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-155-A</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-123-D</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-121-A</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406030-A</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-121-B</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-149-B</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-E</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-F</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-75C</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>97886</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-G</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-153</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-243</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-75C</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F29" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-123-C</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-149-B</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-E</t>
+          <t>US-OR-UMA-UMC-123-C</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-F</t>
+          <t>US-OR-UMA-UMC-117-I</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="G34" s="23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-G</t>
+          <t>US-OR-UMA-UMC-1406025-B</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-117-I</t>
+          <t>US-OR-UMA-UMC-151-H</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="G36" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-H</t>
+          <t>US-OR-UMA-UMC-075B</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-075B</t>
+          <t>US-OR-UMA-UMC-123-B</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G38" s="23" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="B162" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C162" s="22" t="inlineStr">
@@ -7138,11 +7138,11 @@
       </c>
       <c r="F162" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G162" s="21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="B163" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C163" s="22" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="F163" s="21" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G163" s="21" t="n">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B164" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-UMA-UMC-1406015-A</t>
         </is>
       </c>
       <c r="C164" s="22" t="inlineStr">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="F164" s="21" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G164" s="21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B165" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-A</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C165" s="22" t="inlineStr">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="G165" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B166" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C166" s="22" t="inlineStr">
@@ -7278,81 +7278,81 @@
       </c>
       <c r="F166" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G166" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="21" t="inlineStr">
+      <c r="A167" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="inlineStr">
+      <c r="B167" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-E</t>
+        </is>
+      </c>
+      <c r="C167" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D167" s="22" t="inlineStr">
+      <c r="D167" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E167" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F167" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G167" s="21" t="n">
-        <v>1</v>
+      <c r="E167" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F167" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G167" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="21" t="inlineStr">
+      <c r="A168" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B168" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C168" s="22" t="inlineStr">
+      <c r="B168" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-D</t>
+        </is>
+      </c>
+      <c r="C168" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr">
+      <c r="D168" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E168" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F168" s="21" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G168" s="21" t="n">
-        <v>1</v>
+      <c r="E168" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F168" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G168" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B169" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C169" s="26" t="inlineStr">
@@ -7383,11 +7383,11 @@
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G169" s="25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B170" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-UMA-UMC-1406015-C</t>
         </is>
       </c>
       <c r="C170" s="26" t="inlineStr">
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="G170" s="25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="B171" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C171" s="26" t="inlineStr">
@@ -7453,46 +7453,46 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G171" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="25" t="inlineStr">
+      <c r="A172" s="23" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B172" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-149-B</t>
-        </is>
-      </c>
-      <c r="C172" s="26" t="inlineStr">
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C172" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D172" s="26" t="inlineStr">
+      <c r="D172" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E172" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F172" s="25" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="G172" s="25" t="n">
-        <v>1</v>
+      <c r="E172" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F172" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G172" s="23" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="173">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B173" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-C</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C173" s="24" t="inlineStr">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B174" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UMA-UMC-151-G</t>
         </is>
       </c>
       <c r="C174" s="24" t="inlineStr">
@@ -7558,151 +7558,151 @@
       </c>
       <c r="F174" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B175" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-151-G</t>
-        </is>
-      </c>
-      <c r="C175" s="24" t="inlineStr">
+      <c r="A175" s="21" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406043-C</t>
+        </is>
+      </c>
+      <c r="C175" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D175" s="24" t="inlineStr">
+      <c r="D175" s="22" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E175" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F175" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G175" s="23" t="n">
+      <c r="E175" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G175" s="21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="25" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B176" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C176" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D176" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E176" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F176" s="25" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G176" s="25" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B177" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C177" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D177" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E177" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F177" s="23" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="G177" s="23" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="21" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1713-B</t>
+        </is>
+      </c>
+      <c r="C178" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E178" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F178" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G178" s="21" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="21" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B176" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C176" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D176" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E176" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F176" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G176" s="21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B177" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C177" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D177" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E177" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F177" s="25" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G177" s="25" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B178" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C178" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D178" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E178" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F178" s="23" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G178" s="23" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="179">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C179" s="22" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="F179" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G179" s="21" t="n">
@@ -7741,38 +7741,38 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="21" t="inlineStr">
+      <c r="A180" s="25" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B180" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
-        </is>
-      </c>
-      <c r="C180" s="22" t="inlineStr">
+      <c r="B180" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1707</t>
+        </is>
+      </c>
+      <c r="C180" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D180" s="22" t="inlineStr">
+      <c r="D180" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E180" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F180" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G180" s="21" t="n">
-        <v>1</v>
+      <c r="E180" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F180" s="25" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G180" s="25" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="181">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="B181" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C181" s="26" t="inlineStr">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G181" s="25" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B182" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1941</t>
+          <t>US-OR-KLA-KLA-1956</t>
         </is>
       </c>
       <c r="C182" s="26" t="inlineStr">
@@ -7838,46 +7838,46 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G182" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="25" t="inlineStr">
+      <c r="A183" s="23" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B183" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1956</t>
-        </is>
-      </c>
-      <c r="C183" s="26" t="inlineStr">
+      <c r="B183" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C183" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D183" s="26" t="inlineStr">
+      <c r="D183" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E183" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F183" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G183" s="25" t="n">
-        <v>1</v>
+      <c r="E183" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F183" s="23" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="184">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B184" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1946</t>
         </is>
       </c>
       <c r="C184" s="24" t="inlineStr">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="F184" s="23" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G184" s="23" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
@@ -7943,11 +7943,11 @@
       </c>
       <c r="F185" s="23" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="B186" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-KLA-KLA-1361</t>
         </is>
       </c>
       <c r="C186" s="24" t="inlineStr">
@@ -7986,49 +7986,49 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B187" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1361</t>
-        </is>
-      </c>
-      <c r="C187" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D187" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E187" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F187" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>1</v>
+      <c r="A187" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B187" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E187" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G187" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="21" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B188" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-UNI-UCO-140624S</t>
         </is>
       </c>
       <c r="C188" s="22" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="D188" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E188" s="21" t="inlineStr">
@@ -8048,22 +8048,22 @@
       </c>
       <c r="F188" s="21" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="G188" s="21" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="21" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B189" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-121-B</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C189" s="22" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="D189" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E189" s="21" t="inlineStr">
@@ -8093,12 +8093,12 @@
     <row r="190">
       <c r="A190" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B190" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-039</t>
+          <t>US-OR-UNI-UCO-140624N-B</t>
         </is>
       </c>
       <c r="C190" s="26" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D190" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E190" s="25" t="inlineStr">
@@ -8118,22 +8118,22 @@
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G190" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B191" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C191" s="26" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D191" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E191" s="25" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F191" s="25" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G191" s="25" t="n">
@@ -8163,12 +8163,12 @@
     <row r="192">
       <c r="A192" s="23" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-032</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D192" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E192" s="23" t="inlineStr">
@@ -8188,127 +8188,127 @@
       </c>
       <c r="F192" s="23" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G192" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="21" t="inlineStr">
+      <c r="A193" s="23" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B193" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C193" s="22" t="inlineStr">
+      <c r="B193" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1505</t>
+        </is>
+      </c>
+      <c r="C193" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D193" s="22" t="inlineStr">
+      <c r="D193" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E193" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F193" s="21" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G193" s="21" t="n">
-        <v>29</v>
+      <c r="E193" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F193" s="23" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G193" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="21" t="inlineStr">
+      <c r="A194" s="23" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B194" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
-        </is>
-      </c>
-      <c r="C194" s="22" t="inlineStr">
+      <c r="B194" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1513</t>
+        </is>
+      </c>
+      <c r="C194" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="D194" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E194" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F194" s="21" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G194" s="21" t="n">
-        <v>5</v>
+      <c r="E194" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F194" s="23" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="21" t="inlineStr">
+      <c r="A195" s="23" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B195" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624S</t>
-        </is>
-      </c>
-      <c r="C195" s="22" t="inlineStr">
+      <c r="B195" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1495</t>
+        </is>
+      </c>
+      <c r="C195" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D195" s="22" t="inlineStr">
+      <c r="D195" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E195" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F195" s="21" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="G195" s="21" t="n">
+      <c r="E195" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F195" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G195" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="21" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B196" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C196" s="22" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D196" s="22" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E196" s="21" t="inlineStr">
@@ -8328,137 +8328,137 @@
       </c>
       <c r="F196" s="21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G196" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="23" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B197" s="24" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C197" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D197" s="24" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E197" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F197" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B197" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C197" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D197" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E197" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F197" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G197" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="198">
-      <c r="A198" s="23" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B198" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1497</t>
-        </is>
-      </c>
-      <c r="C198" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D198" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E198" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F198" s="23" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="G198" s="23" t="n">
-        <v>1</v>
+      <c r="A198" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B198" s="26" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C198" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D198" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E198" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F198" s="25" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G198" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="23" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B199" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1505</t>
-        </is>
-      </c>
-      <c r="C199" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D199" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E199" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F199" s="23" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G199" s="23" t="n">
-        <v>1</v>
+      <c r="A199" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B199" s="26" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C199" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D199" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E199" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F199" s="25" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G199" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>Cooper Spur North</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D200" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E200" s="23" t="inlineStr">
@@ -8468,32 +8468,32 @@
       </c>
       <c r="F200" s="23" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1495</t>
+          <t>Cooper Spur South</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D201" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E201" s="23" t="inlineStr">
@@ -8503,67 +8503,67 @@
       </c>
       <c r="F201" s="23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B202" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C202" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D202" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E202" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F202" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G202" s="21" t="n">
-        <v>2</v>
+      <c r="A202" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B202" s="24" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C202" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D202" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E202" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F202" s="23" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="23" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D203" s="24" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E203" s="23" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F203" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
@@ -8581,49 +8581,49 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="21" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B204" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
-        </is>
-      </c>
-      <c r="C204" s="22" t="inlineStr">
+      <c r="A204" s="25" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B204" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C204" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D204" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E204" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F204" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G204" s="21" t="n">
-        <v>1</v>
+      <c r="D204" s="26" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E204" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F204" s="25" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G204" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="25" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B205" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C205" s="26" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D205" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E205" s="25" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F205" s="25" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G205" s="25" t="n">
@@ -8651,94 +8651,94 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B206" s="26" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C206" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D206" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E206" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F206" s="25" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G206" s="25" t="n">
-        <v>4</v>
+      <c r="A206" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B206" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1421</t>
+        </is>
+      </c>
+      <c r="C206" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D206" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E206" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F206" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G206" s="23" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B207" s="26" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C207" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D207" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E207" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F207" s="25" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G207" s="25" t="n">
-        <v>2</v>
+      <c r="A207" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B207" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1436</t>
+        </is>
+      </c>
+      <c r="C207" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D207" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E207" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F207" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G207" s="23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="23" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D208" s="24" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E208" s="23" t="inlineStr">
@@ -8748,32 +8748,32 @@
       </c>
       <c r="F208" s="23" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G208" s="23" t="n">
-        <v>158</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="23" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>Cooper Spur South</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D209" s="24" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E209" s="23" t="inlineStr">
@@ -8783,67 +8783,67 @@
       </c>
       <c r="F209" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G209" s="23" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B210" s="24" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C210" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D210" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E210" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F210" s="23" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G210" s="23" t="n">
-        <v>4</v>
+      <c r="A210" s="25" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B210" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C210" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D210" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E210" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F210" s="25" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G210" s="25" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="23" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>White River</t>
+          <t>US-OR-KLA-KLA-2261</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D211" s="24" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E211" s="23" t="inlineStr">
@@ -8853,102 +8853,102 @@
       </c>
       <c r="F211" s="23" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G211" s="23" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B212" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1435</t>
-        </is>
-      </c>
-      <c r="C212" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D212" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E212" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F212" s="25" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="G212" s="25" t="n">
-        <v>6</v>
+      <c r="A212" s="23" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B212" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1936</t>
+        </is>
+      </c>
+      <c r="C212" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D212" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E212" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F212" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G212" s="23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B213" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C213" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D213" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E213" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F213" s="25" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G213" s="25" t="n">
+      <c r="A213" s="23" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B213" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2256</t>
+        </is>
+      </c>
+      <c r="C213" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D213" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E213" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F213" s="23" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="23" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B214" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C214" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D214" s="24" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E214" s="23" t="inlineStr">
@@ -8958,242 +8958,242 @@
       </c>
       <c r="F214" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G214" s="23" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="23" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
         <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D215" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E215" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F215" s="23" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G215" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="25" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B216" s="26" t="inlineStr">
+        <is>
+          <t>WRR</t>
+        </is>
+      </c>
+      <c r="C216" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D216" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E216" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F216" s="25" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G216" s="25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="25" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B217" s="26" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C217" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D217" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E217" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F217" s="25" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G217" s="25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="23" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B218" s="24" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="C218" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D218" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E218" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F218" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G218" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B219" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C219" s="26" t="inlineStr">
+        <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D215" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E215" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F215" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G215" s="23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="23" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B216" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1437</t>
-        </is>
-      </c>
-      <c r="C216" s="24" t="inlineStr">
+      <c r="D219" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E219" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F219" s="25" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G219" s="25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B220" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-121-B</t>
+        </is>
+      </c>
+      <c r="C220" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D216" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E216" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F216" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G216" s="23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="23" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B217" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1438</t>
-        </is>
-      </c>
-      <c r="C217" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D217" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E217" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F217" s="23" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G217" s="23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B218" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C218" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D218" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E218" s="25" t="inlineStr">
+      <c r="D220" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E220" s="25" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F218" s="25" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G218" s="25" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B219" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-2261</t>
-        </is>
-      </c>
-      <c r="C219" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D219" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E219" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F219" s="23" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G219" s="23" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B220" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1936</t>
-        </is>
-      </c>
-      <c r="C220" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D220" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E220" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F220" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G220" s="23" t="n">
-        <v>2</v>
+      <c r="F220" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G220" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="23" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B221" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2256</t>
+          <t>US-OR-UMA-UMC-032</t>
         </is>
       </c>
       <c r="C221" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D221" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E221" s="23" t="inlineStr">
@@ -9203,32 +9203,32 @@
       </c>
       <c r="F221" s="23" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G221" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="23" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B222" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1931</t>
+          <t>US-OR-UMA-UMC-123-B</t>
         </is>
       </c>
       <c r="C222" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D222" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E222" s="23" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F222" s="23" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G222" s="23" t="n">
@@ -9248,22 +9248,22 @@
     <row r="223">
       <c r="A223" s="23" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B223" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-UMA-UMC-1406025-B</t>
         </is>
       </c>
       <c r="C223" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D223" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E223" s="23" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="F223" s="23" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G223" s="23" t="n">
@@ -9283,22 +9283,22 @@
     <row r="224">
       <c r="A224" s="25" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B224" s="26" t="inlineStr">
         <is>
-          <t>WRR</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C224" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D224" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E224" s="25" t="inlineStr">
@@ -9308,67 +9308,67 @@
       </c>
       <c r="F224" s="25" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G224" s="25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="25" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B225" s="26" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C225" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D225" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E225" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F225" s="25" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G225" s="25" t="n">
-        <v>3</v>
+      <c r="A225" s="23" t="inlineStr">
+        <is>
+          <t>97848</t>
+        </is>
+      </c>
+      <c r="B225" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-023</t>
+        </is>
+      </c>
+      <c r="C225" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D225" s="24" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="E225" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F225" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G225" s="23" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="23" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="B226" s="24" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>BC1</t>
         </is>
       </c>
       <c r="C226" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Burnt Creek Fire</t>
         </is>
       </c>
       <c r="D226" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Wallowa</t>
         </is>
       </c>
       <c r="E226" s="23" t="inlineStr">
@@ -9378,32 +9378,32 @@
       </c>
       <c r="F226" s="23" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="G226" s="23" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="23" t="inlineStr">
         <is>
-          <t>97848</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B227" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C227" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D227" s="24" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E227" s="23" t="inlineStr">
@@ -9413,32 +9413,32 @@
       </c>
       <c r="F227" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="G227" s="23" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="23" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B228" s="24" t="inlineStr">
         <is>
-          <t>BC1</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C228" s="24" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D228" s="24" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E228" s="23" t="inlineStr">
@@ -9448,32 +9448,32 @@
       </c>
       <c r="F228" s="23" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G228" s="23" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="23" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B229" s="24" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C229" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D229" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E229" s="23" t="inlineStr">
@@ -9483,32 +9483,32 @@
       </c>
       <c r="F229" s="23" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G229" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B230" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-WHE-WHH-090-A</t>
         </is>
       </c>
       <c r="C230" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D230" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Wheeler</t>
         </is>
       </c>
       <c r="E230" s="23" t="inlineStr">
@@ -9518,32 +9518,32 @@
       </c>
       <c r="F230" s="23" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G230" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B231" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-GRA-GRN-023</t>
         </is>
       </c>
       <c r="C231" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D231" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E231" s="23" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="F231" s="23" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G231" s="23" t="n">
@@ -9563,22 +9563,22 @@
     <row r="232">
       <c r="A232" s="23" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B232" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-090-A</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C232" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D232" s="24" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E232" s="23" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F232" s="23" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G232" s="23" t="n">
@@ -9598,22 +9598,22 @@
     <row r="233">
       <c r="A233" s="23" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B233" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C233" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D233" s="24" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E233" s="23" t="inlineStr">
@@ -9630,78 +9630,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="23" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B234" s="24" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C234" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D234" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E234" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F234" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G234" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="23" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B235" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C235" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D235" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E235" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F235" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G235" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" ht="60" customHeight="1">
-      <c r="A237" s="27" t="inlineStr">
+    <row r="235" ht="60" customHeight="1">
+      <c r="A235" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -9709,7 +9639,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A237:G237"/>
+    <mergeCell ref="A235:G235"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
